--- a/artfynd/A 59611-2024 artfynd.xlsx
+++ b/artfynd/A 59611-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122306973</v>
+        <v>122306756</v>
       </c>
       <c r="B2" t="n">
-        <v>90797</v>
+        <v>78645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Orrflon, Orrflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441688</v>
+        <v>441710</v>
       </c>
       <c r="R2" t="n">
-        <v>7038042</v>
+        <v>7038072</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122306227</v>
+        <v>122306973</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>90797</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,34 +818,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Orrflon, Orrflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441670</v>
+        <v>441688</v>
       </c>
       <c r="R3" t="n">
-        <v>7038115</v>
+        <v>7038042</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,12 +911,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122305999</v>
+        <v>122306270</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,34 +950,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrflon, Orrflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441566</v>
+        <v>441649</v>
       </c>
       <c r="R4" t="n">
-        <v>7038173</v>
+        <v>7038107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1038,12 +1043,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,7 +1066,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122306756</v>
+        <v>122306227</v>
       </c>
       <c r="B5" t="n">
         <v>78645</v>
@@ -1101,10 +1106,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441710</v>
+        <v>441670</v>
       </c>
       <c r="R5" t="n">
-        <v>7038072</v>
+        <v>7038115</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1188,10 +1193,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122306270</v>
+        <v>122305999</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>78645</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1204,39 +1209,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Orrflon, Orrflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441649</v>
+        <v>441566</v>
       </c>
       <c r="R6" t="n">
-        <v>7038107</v>
+        <v>7038173</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122349604</v>
+        <v>122349579</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,21 +1336,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441551</v>
+        <v>441700</v>
       </c>
       <c r="R7" t="n">
-        <v>7038179</v>
+        <v>7038044</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122349580</v>
+        <v>122349604</v>
       </c>
       <c r="B8" t="n">
-        <v>74747</v>
+        <v>78645</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441690</v>
+        <v>441551</v>
       </c>
       <c r="R8" t="n">
-        <v>7038085</v>
+        <v>7038179</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122349579</v>
+        <v>122349580</v>
       </c>
       <c r="B9" t="n">
         <v>74747</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441700</v>
+        <v>441690</v>
       </c>
       <c r="R9" t="n">
-        <v>7038044</v>
+        <v>7038085</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122360806</v>
+        <v>122360817</v>
       </c>
       <c r="B11" t="n">
-        <v>57390</v>
+        <v>90797</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441488</v>
+        <v>441638</v>
       </c>
       <c r="R11" t="n">
-        <v>7038256</v>
+        <v>7038175</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,11 +1804,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122360819</v>
+        <v>122360806</v>
       </c>
       <c r="B12" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,21 +1846,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441489</v>
+        <v>441488</v>
       </c>
       <c r="R12" t="n">
-        <v>7038254</v>
+        <v>7038256</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1910,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,7 +1937,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122360820</v>
+        <v>122360819</v>
       </c>
       <c r="B13" t="n">
         <v>78645</v>
@@ -1976,19 +1971,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Orrflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441608</v>
+        <v>441489</v>
       </c>
       <c r="R13" t="n">
-        <v>7038209</v>
+        <v>7038254</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,7 +2026,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2053,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122360817</v>
+        <v>122360820</v>
       </c>
       <c r="B14" t="n">
-        <v>90797</v>
+        <v>78645</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,34 +2060,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Orrflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441638</v>
+        <v>441608</v>
       </c>
       <c r="R14" t="n">
-        <v>7038175</v>
+        <v>7038209</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,12 +2125,18 @@
           <t>2025-01-25</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
